--- a/regression_deneme/regression_with_nn/yeşildere caddesi_monthly_true_and_predicted_test.xlsx
+++ b/regression_deneme/regression_with_nn/yeşildere caddesi_monthly_true_and_predicted_test.xlsx
@@ -461,7 +461,7 @@
         <v>82</v>
       </c>
       <c r="D2" t="n">
-        <v>69.9821785875793</v>
+        <v>72.23790869555739</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>65</v>
       </c>
       <c r="D3" t="n">
-        <v>69.59532713134361</v>
+        <v>66.30568452748736</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>49</v>
       </c>
       <c r="D4" t="n">
-        <v>58.02905939120309</v>
+        <v>59.60105826353804</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>44.59406707457343</v>
+        <v>49.51996200689403</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>37.82250535738668</v>
+        <v>40.19208478285884</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>57</v>
       </c>
       <c r="D7" t="n">
-        <v>62.49401785188321</v>
+        <v>61.49979505266948</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>58.2166355948798</v>
+        <v>50.69672667161225</v>
       </c>
     </row>
   </sheetData>
